--- a/Input/lib_villes.xlsx
+++ b/Input/lib_villes.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>code</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>طنجة</t>
+  </si>
+  <si>
+    <t>Tetouan</t>
+  </si>
+  <si>
+    <t>Tangier</t>
   </si>
 </sst>
 </file>
@@ -427,7 +433,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -477,7 +483,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -491,7 +497,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
